--- a/output/StructureDefinition-BRProcedimentoRealizado-1.0.xlsx
+++ b/output/StructureDefinition-BRProcedimentoRealizado-1.0.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5886" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5884" uniqueCount="700">
   <si>
     <t>Property</t>
   </si>
@@ -1247,6 +1247,15 @@
     <t>gender</t>
   </si>
   <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>Sexo biológico obtido por meio de exame clínico ou de outros métodos diagnósticos referente ao indivíduo da hipótese de impossibilidade de identificação.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRSexo-1.0</t>
+  </si>
+  <si>
     <t>Procedure.subject.extension:unidentifiedPatient.extension:gender.id</t>
   </si>
   <si>
@@ -1275,6 +1284,12 @@
   </si>
   <si>
     <t>birthYear</t>
+  </si>
+  <si>
+    <t>Ano de nascimento estimado</t>
+  </si>
+  <si>
+    <t>Estimativa do ano de nascimento por meio de observação direta da idade do indivíduo na hipótese de impossibilidade de identificação..</t>
   </si>
   <si>
     <t>Procedure.subject.extension:unidentifiedPatient.extension:birthYear.id</t>
@@ -1297,6 +1312,15 @@
   </si>
   <si>
     <t>reason</t>
+  </si>
+  <si>
+    <t>Justificativa da impossibilidade de identificação do indivíduo</t>
+  </si>
+  <si>
+    <t>Razão pela qual não foi possível obter os dados de identificação do indivíduo no contato assistencial.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRJustificativaIndividuoNaoIdentificado-1.0</t>
   </si>
   <si>
     <t>Procedure.subject.extension:unidentifiedPatient.extension:reason.id</t>
@@ -2507,7 +2531,7 @@
     <col min="23" max="23" width="16.40625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="15.85546875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="87.265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.64453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.20703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.2734375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.1171875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.56640625" customWidth="true" bestFit="true"/>
@@ -9390,10 +9414,10 @@
         <v>131</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>132</v>
+        <v>396</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>133</v>
+        <v>397</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9420,13 +9444,11 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>77</v>
+        <v>398</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -9473,10 +9495,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9585,10 +9607,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9699,10 +9721,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9813,10 +9835,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9925,13 +9947,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>392</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>77</v>
@@ -9956,10 +9978,10 @@
         <v>131</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>132</v>
+        <v>409</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>133</v>
+        <v>410</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10039,10 +10061,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10151,10 +10173,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10265,10 +10287,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10308,7 +10330,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>77</v>
@@ -10379,10 +10401,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10405,7 +10427,7 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>169</v>
@@ -10491,13 +10513,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>392</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>77</v>
@@ -10522,10 +10544,10 @@
         <v>131</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>132</v>
+        <v>418</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>133</v>
+        <v>419</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10552,13 +10574,11 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>77</v>
+        <v>420</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
@@ -10605,10 +10625,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10717,10 +10737,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10831,10 +10851,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10874,7 +10894,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>77</v>
@@ -10945,10 +10965,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11057,10 +11077,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11100,7 +11120,7 @@
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>77</v>
@@ -11171,10 +11191,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11197,7 +11217,7 @@
         <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>169</v>
@@ -11283,10 +11303,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11312,13 +11332,13 @@
         <v>146</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11368,7 +11388,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11377,7 +11397,7 @@
         <v>87</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>98</v>
@@ -11397,10 +11417,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11426,13 +11446,13 @@
         <v>100</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11458,13 +11478,13 @@
         <v>77</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>77</v>
@@ -11482,7 +11502,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11511,10 +11531,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11540,13 +11560,13 @@
         <v>178</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11596,7 +11616,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11614,7 +11634,7 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -11625,10 +11645,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11737,10 +11757,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11851,10 +11871,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11967,10 +11987,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11996,7 +12016,7 @@
         <v>200</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="M84" t="s" s="2">
         <v>202</v>
@@ -12030,13 +12050,13 @@
         <v>77</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>77</v>
@@ -12083,10 +12103,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12199,10 +12219,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12228,10 +12248,10 @@
         <v>146</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>280</v>
@@ -12313,10 +12333,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12425,10 +12445,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12539,10 +12559,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12568,13 +12588,13 @@
         <v>146</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12624,7 +12644,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12653,10 +12673,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12679,16 +12699,16 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12738,7 +12758,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12753,24 +12773,24 @@
         <v>98</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12793,16 +12813,16 @@
         <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12852,7 +12872,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12867,24 +12887,24 @@
         <v>98</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12907,13 +12927,13 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12964,7 +12984,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12982,10 +13002,10 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>77</v>
@@ -12993,10 +13013,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13019,13 +13039,13 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13076,7 +13096,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13094,10 +13114,10 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>77</v>
@@ -13105,10 +13125,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13131,13 +13151,13 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13188,7 +13208,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13203,10 +13223,10 @@
         <v>98</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
@@ -13217,10 +13237,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13329,10 +13349,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13439,13 +13459,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>77</v>
@@ -13467,13 +13487,13 @@
         <v>77</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13553,14 +13573,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13582,10 +13602,10 @@
         <v>131</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>156</v>
@@ -13640,7 +13660,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13669,10 +13689,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13698,14 +13718,14 @@
         <v>200</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>77</v>
@@ -13733,10 +13753,10 @@
         <v>194</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>77</v>
@@ -13754,7 +13774,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13769,24 +13789,24 @@
         <v>98</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13895,10 +13915,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14009,10 +14029,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14125,10 +14145,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14237,10 +14257,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14351,10 +14371,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14467,10 +14487,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14581,10 +14601,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14695,10 +14715,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14809,10 +14829,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14925,10 +14945,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15041,10 +15061,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15067,17 +15087,17 @@
         <v>80</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>77</v>
@@ -15126,7 +15146,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>87</v>
@@ -15141,24 +15161,24 @@
         <v>98</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15267,10 +15287,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15381,10 +15401,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15410,13 +15430,13 @@
         <v>146</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15466,7 +15486,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -15475,7 +15495,7 @@
         <v>87</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>98</v>
@@ -15495,10 +15515,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15524,13 +15544,13 @@
         <v>100</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15556,13 +15576,13 @@
         <v>77</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>77</v>
@@ -15580,7 +15600,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15609,10 +15629,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15638,13 +15658,13 @@
         <v>178</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15694,7 +15714,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15712,7 +15732,7 @@
         <v>77</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>77</v>
@@ -15723,10 +15743,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15835,10 +15855,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15949,10 +15969,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16065,10 +16085,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16094,7 +16114,7 @@
         <v>200</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="M120" t="s" s="2">
         <v>202</v>
@@ -16128,13 +16148,13 @@
         <v>77</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>77</v>
@@ -16181,10 +16201,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16297,10 +16317,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16326,10 +16346,10 @@
         <v>146</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>280</v>
@@ -16411,10 +16431,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16523,10 +16543,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16637,10 +16657,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16666,13 +16686,13 @@
         <v>146</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16722,7 +16742,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16751,10 +16771,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16777,17 +16797,17 @@
         <v>77</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
@@ -16836,7 +16856,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16854,7 +16874,7 @@
         <v>77</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>77</v>
@@ -16865,10 +16885,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16977,10 +16997,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17091,10 +17111,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17120,13 +17140,13 @@
         <v>146</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17176,7 +17196,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17185,7 +17205,7 @@
         <v>87</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>98</v>
@@ -17205,10 +17225,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17234,13 +17254,13 @@
         <v>100</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -17266,13 +17286,13 @@
         <v>77</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>77</v>
@@ -17290,7 +17310,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17319,10 +17339,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17348,13 +17368,13 @@
         <v>178</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -17404,7 +17424,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17422,7 +17442,7 @@
         <v>77</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>77</v>
@@ -17433,10 +17453,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17545,10 +17565,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17659,10 +17679,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17775,10 +17795,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17804,7 +17824,7 @@
         <v>200</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="M135" t="s" s="2">
         <v>202</v>
@@ -17838,13 +17858,13 @@
         <v>77</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>77</v>
@@ -17891,10 +17911,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18007,10 +18027,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18036,10 +18056,10 @@
         <v>146</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="N137" t="s" s="2">
         <v>280</v>
@@ -18121,10 +18141,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18233,10 +18253,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18347,10 +18367,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18376,13 +18396,13 @@
         <v>146</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -18432,7 +18452,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18461,10 +18481,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18487,17 +18507,17 @@
         <v>80</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>77</v>
@@ -18546,7 +18566,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -18564,10 +18584,10 @@
         <v>77</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>77</v>
@@ -18575,10 +18595,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18604,13 +18624,13 @@
         <v>200</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -18639,10 +18659,10 @@
         <v>340</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>77</v>
@@ -18660,7 +18680,7 @@
         <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -18675,13 +18695,13 @@
         <v>98</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>77</v>
@@ -18689,10 +18709,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18715,16 +18735,16 @@
         <v>80</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -18774,7 +18794,7 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -18789,13 +18809,13 @@
         <v>98</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>77</v>
@@ -18803,10 +18823,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18832,13 +18852,13 @@
         <v>200</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -18867,10 +18887,10 @@
         <v>340</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>77</v>
@@ -18888,7 +18908,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -18906,21 +18926,21 @@
         <v>77</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>602</v>
+        <v>610</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18946,13 +18966,13 @@
         <v>200</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -18981,10 +19001,10 @@
         <v>340</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>77</v>
@@ -19002,7 +19022,7 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -19020,7 +19040,7 @@
         <v>77</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>77</v>
@@ -19031,10 +19051,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19057,16 +19077,16 @@
         <v>77</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -19116,7 +19136,7 @@
         <v>77</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>78</v>
@@ -19134,7 +19154,7 @@
         <v>77</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>77</v>
@@ -19145,10 +19165,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19174,13 +19194,13 @@
         <v>200</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -19209,10 +19229,10 @@
         <v>340</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>77</v>
@@ -19230,7 +19250,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -19248,7 +19268,7 @@
         <v>77</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>77</v>
@@ -19259,10 +19279,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19285,17 +19305,17 @@
         <v>77</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>77</v>
@@ -19344,7 +19364,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19362,7 +19382,7 @@
         <v>77</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>77</v>
@@ -19373,10 +19393,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19402,10 +19422,10 @@
         <v>200</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -19435,10 +19455,10 @@
         <v>340</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>77</v>
@@ -19456,7 +19476,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -19474,7 +19494,7 @@
         <v>77</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>77</v>
@@ -19485,10 +19505,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19511,13 +19531,13 @@
         <v>77</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -19568,7 +19588,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19583,24 +19603,24 @@
         <v>98</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>640</v>
+        <v>648</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19709,10 +19729,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19823,10 +19843,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19849,16 +19869,16 @@
         <v>80</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -19908,7 +19928,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -19926,7 +19946,7 @@
         <v>77</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>77</v>
@@ -19937,10 +19957,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19963,13 +19983,13 @@
         <v>80</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -20020,7 +20040,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -20038,7 +20058,7 @@
         <v>77</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>77</v>
@@ -20049,10 +20069,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20075,13 +20095,13 @@
         <v>80</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -20132,7 +20152,7 @@
         <v>77</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>87</v>
@@ -20150,7 +20170,7 @@
         <v>77</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>77</v>
@@ -20161,10 +20181,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20187,13 +20207,13 @@
         <v>77</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -20244,7 +20264,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -20262,7 +20282,7 @@
         <v>77</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>77</v>
@@ -20273,10 +20293,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20385,10 +20405,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20499,14 +20519,14 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
@@ -20528,10 +20548,10 @@
         <v>131</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="N159" t="s" s="2">
         <v>156</v>
@@ -20586,7 +20606,7 @@
         <v>77</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>78</v>
@@ -20615,10 +20635,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20644,10 +20664,10 @@
         <v>200</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -20677,10 +20697,10 @@
         <v>110</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>77</v>
@@ -20698,7 +20718,7 @@
         <v>77</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -20716,7 +20736,7 @@
         <v>77</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>77</v>
@@ -20727,10 +20747,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20753,13 +20773,13 @@
         <v>77</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -20810,7 +20830,7 @@
         <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>87</v>
@@ -20828,7 +20848,7 @@
         <v>77</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>77</v>
@@ -20839,10 +20859,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20865,19 +20885,19 @@
         <v>77</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>77</v>
@@ -20926,7 +20946,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -20944,7 +20964,7 @@
         <v>77</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>77</v>
@@ -20955,10 +20975,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20984,13 +21004,13 @@
         <v>200</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -21019,10 +21039,10 @@
         <v>340</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>77</v>
@@ -21040,7 +21060,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -21058,7 +21078,7 @@
         <v>77</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>77</v>
